--- a/Result/profitability/2356.xlsx
+++ b/Result/profitability/2356.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.56625</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>5.195</v>
+        <v>5.065</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5675</v>
+        <v>0.62125</v>
       </c>
       <c r="N3" t="n">
-        <v>5.06125</v>
+        <v>4.95375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.57875</v>
+        <v>0.65625</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7025</v>
+        <v>4.4825</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5912500000000001</v>
+        <v>0.65125</v>
       </c>
       <c r="N5" t="n">
-        <v>4.42875</v>
+        <v>4.32125</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.58375</v>
+        <v>0.625</v>
       </c>
       <c r="N6" t="n">
-        <v>4.21375</v>
+        <v>4.1125</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.53</v>
+        <v>0.59375</v>
       </c>
       <c r="N7" t="n">
-        <v>4.02</v>
+        <v>3.8975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>0.505</v>
+        <v>0.55625</v>
       </c>
       <c r="N8" t="n">
-        <v>3.83875</v>
+        <v>3.7325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.41</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4974999999999999</v>
+        <v>0.4975</v>
       </c>
       <c r="N10" t="n">
         <v>3.845</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>269857</v>
+      </c>
+      <c r="D75" t="n">
+        <v>258441</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11416</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4741</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>276</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5017</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3895</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.67625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6029411764705883</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8499999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1673228346456692</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7868852459016396</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.8599999999999994</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1689587426326129</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
